--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_27-01-2026.xlsx
@@ -578,12 +578,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-pir-tb-ga-xr?_pos=1&amp;_sid=22d5094c4&amp;_ss=r (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>£10.25</t>
+          <t>£11.28</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>£9.59</t>
+          <t>£10.55</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>£9.47</t>
+          <t>£10.15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>£11.86</t>
+          <t>£13.05</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£11.09</t>
+          <t>£12.20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>£11.40</t>
+          <t>£12.55</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>£14.59</t>
+          <t>£16.05</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>£14.01</t>
+          <t>£15.41</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£13.81</t>
+          <t>£14.62</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>£16.21</t>
+          <t>£17.83</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -869,17 +869,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>£16.01</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>£14.55</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>£14.55</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>£14.55</t>
+          <t>£15.31</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>£19.42</t>
+          <t>£21.36</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>£18.15</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>£18.04</t>
+          <t>£19.71</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>£21.03</t>
+          <t>£23.13</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>£20.30</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>£20.13</t>
+          <t>£20.98</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>£21.39</t>
+          <t>£23.53</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>£20.15</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>£20.16</t>
+          <t>£22.11</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>£23.54</t>
+          <t>£25.89</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>£23.30</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/80mm-celotex/</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>£22.75</t>
+          <t>£24.04</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>£30.82</t>
+          <t>£33.90</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>£25.45</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>£24.95</t>
+          <t>£27.44</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>£27.02</t>
+          <t>£29.72</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>£27.49</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>£24.99</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>£24.99</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>£24.38</t>
+          <t>£26.34</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>£50.96</t>
+          <t>£56.06</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£31.99</t>
+          <t>£35.19</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>£30.49</t>
+          <t>£31.98</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1550,14 +1550,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>£30.45</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>£30.45</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>£34.95</t>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>£32.54</t>
+          <t>£35.79</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>£30.45</t>
+          <t>£33.50</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>£30.27</t>
+          <t>£32.75</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>£37.14</t>
+          <t>£40.85</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>£37.40</t>
+          <t>£41.14</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£36.18</t>
+          <t>£37.82</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>£40.25</t>
+          <t>£44.28</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>£38.50</t>
+          <t>£42.35</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>£37.59</t>
+          <t>£38.42</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>£39.47</t>
+          <t>£43.42</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>£37.50</t>
+          <t>£41.25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>£36.83</t>
+          <t>£39.12</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>£959.7</t>
+          <t>£1055.68</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>£719.88</t>
+          <t>£791.88</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>£954.24</t>
+          <t>£804.0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>£1164.06</t>
+          <t>£1280.46</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>£935.88</t>
+          <t>£1029.48</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>£1043.52</t>
+          <t>£940.8</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>£48.24</t>
+          <t>£53.06</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>£26.60</t>
+          <t>£29.26</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>£25.97</t>
+          <t>£26.08</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-pl4000-insulation-boards?variant=42844828827885 (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>£58.53</t>
+          <t>£64.38</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>£32.35</t>
+          <t>£35.59</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£30.26</t>
+          <t>£31.75</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£35.57</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>£66.08</t>
+          <t>£72.69</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>£35.55</t>
+          <t>£39.10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>£68.87</t>
+          <t>£75.76</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>£40.40</t>
+          <t>£44.44</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£39.13</t>
+          <t>£40.82</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>£65.48</t>
+          <t>£72.03</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>£43.79</t>
+          <t>£48.17</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>£63.59</t>
+          <t>£69.95</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>£43.25</t>
+          <t>£47.58</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£925.00</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>£1439.04</t>
+          <t>£1582.88</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>£924.00</t>
+          <t>£1,016.40</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>£62.02</t>
+          <t>£68.22</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>£42.80</t>
+          <t>£47.08</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>£1057.71</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>£1588.8</t>
+          <t>£1747.68</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>£1152.0</t>
+          <t>£1267.2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>£1127.68</t>
+          <t>£1224.64</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>£1700.0</t>
+          <t>£1870.08</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>£1280.0</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>£1252.8</t>
+          <t>£1377.12</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>£1804.16</t>
+          <t>£1984.64</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1280.0</t>
+          <t>£1408.0</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
